--- a/sheets/investing/dividend-log/dividend-log.xlsx
+++ b/sheets/investing/dividend-log/dividend-log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\000_drive_drive\600_PROJECTS\modelstack\sheets\investing\dividend-log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\000_drive_drive\300_WORK\xAI\002_xAI\project\excel-scraping\task_016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86787FC4-3016-4A02-89DA-6584D94124FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC41537F-68E3-4813-AA20-3ED69E3D4E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35520" yWindow="2145" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Holdings &amp; Settings" sheetId="1" r:id="rId1"/>
@@ -68,9 +68,6 @@
     <t>Yield on Cost</t>
   </si>
   <si>
-    <t>At a glance</t>
-  </si>
-  <si>
     <t>JNJ</t>
   </si>
   <si>
@@ -219,6 +216,9 @@
   </si>
   <si>
     <t>Cash-Take Annual Income</t>
+  </si>
+  <si>
+    <t>Overview</t>
   </si>
 </sst>
 </file>
@@ -228,9 +228,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,25 +254,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF4472C4"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -306,7 +287,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -345,36 +326,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FFD9D9D9"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -403,58 +371,37 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -478,44 +425,371 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
+  <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="103"/>
+      <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="3"/>
+      <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reinvestment History'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Shares Outstanding</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Reinvestment History'!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reinvestment History'!$F$2:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>416.6112956810631</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>416.6112956810631</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>417.5447963084157</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>419.14777136424055</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>419.14777136424055</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>420.08034313524752</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>421.67843594395504</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>421.67843594395504</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>422.61066253108623</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>424.2058357471625</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>424.2058357471625</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>425.14000685600922</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAD1-45F2-8DD2-2427E8746592}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                  <a:alpha val="33000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="1780822399"/>
+        <c:axId val="1780822879"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1780822399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst/>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Monthly div cash</a:t>
-            </a:r>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
+        </c:txPr>
+        <c:crossAx val="1780822879"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1780822879"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1780822399"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -547,21 +821,11 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.6378896882494004E-2"/>
-          <c:y val="0.12280701754385964"/>
-          <c:w val="0.94724220623501199"/>
-          <c:h val="0.77544619422572181"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -576,464 +840,34 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="40000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="40000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="51000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="51000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="62000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="62000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="73000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="73000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="83000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="83000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:shade val="94000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="6"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="95000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="95000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="84000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="8"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="74000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="74000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="9"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="63000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="63000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="10"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="52000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="52000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="11"/>
-            <c:invertIfNegative val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="41000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="41000"/>
-                      <a:lumMod val="84000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-114E-4846-9597-339F5F5B6DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
+          <c:spPr>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="84000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="1"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="20000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="#,##0" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1048,9 +882,9 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1178,7 +1012,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2648-4B38-A75B-1437DED9F3FB}"/>
+              <c16:uniqueId val="{00000000-4D31-42C7-BE8A-67A761414EBA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1192,11 +1026,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="41"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
+        <c:axId val="92640"/>
+        <c:axId val="91200"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10"/>
+        <c:axId val="92640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1234,80 +1068,25 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="100"/>
+        <c:crossAx val="91200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="100"/>
+        <c:axId val="91200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Dollars</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:crossAx val="92640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1321,7 +1100,14 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -1370,11 +1156,11 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
+  <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
@@ -1385,33 +1171,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Income by ticker</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1424,9 +1184,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1439,20 +1202,8 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.12945304655709983"/>
-          <c:y val="0.14106939704209329"/>
-          <c:w val="0.8105320391997981"/>
-          <c:h val="0.64926786882015186"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
+      <c:layout/>
+      <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1468,157 +1219,134 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
           <c:dPt>
             <c:idx val="0"/>
-            <c:invertIfNegative val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="50000"/>
-                      <a:satMod val="300000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="35000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="37000"/>
-                      <a:satMod val="300000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:tint val="15000"/>
-                      <a:satMod val="350000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="16200000" scaled="1"/>
-              </a:gradFill>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:shade val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:round/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="38000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-94A0-4726-AF35-2990ACB92585}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:invertIfNegative val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent2">
-                      <a:tint val="50000"/>
-                      <a:satMod val="300000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="35000">
-                    <a:schemeClr val="accent2">
-                      <a:tint val="37000"/>
-                      <a:satMod val="300000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent2">
-                      <a:tint val="15000"/>
-                      <a:satMod val="350000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="16200000" scaled="1"/>
-              </a:gradFill>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:shade val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:round/>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="38000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-94A0-4726-AF35-2990ACB92585}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:invertIfNegative val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent3">
-                      <a:tint val="50000"/>
-                      <a:satMod val="300000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="35000">
-                    <a:schemeClr val="accent3">
-                      <a:tint val="37000"/>
-                      <a:satMod val="300000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent3">
-                      <a:tint val="15000"/>
-                      <a:satMod val="350000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="16200000" scaled="1"/>
-              </a:gradFill>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:shade val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:round/>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="38000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-94A0-4726-AF35-2990ACB92585}"/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
-          </c:dPt>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Income &amp; Yield Summary'!$A$10:$A$12</c:f>
@@ -1656,184 +1384,22 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-91D2-49BD-B075-AE93CAC4FD9B}"/>
+              <c16:uniqueId val="{00000000-D1BD-4F1D-A10C-FA22304F84F2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="100"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="50000"/>
-                        <a:lumOff val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Dollars</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="100"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="100"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1842,9 +1408,45 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1852,9 +1454,9 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -1880,8 +1482,42 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -1925,7 +1561,585 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" spc="20" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+            <a:alpha val="33000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="204">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2492,198 +2706,236 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="219">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
         <a:solidFill>
           <a:schemeClr val="dk1">
             <a:lumMod val="25000"/>
             <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="15875" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
+            <a:alpha val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="2"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
@@ -2702,17 +2954,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2729,15 +2981,15 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2753,7 +3005,7 @@
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
@@ -2772,40 +3024,53 @@
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
@@ -2816,12 +3081,24 @@
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2835,95 +3112,7 @@
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
@@ -2931,30 +3120,126 @@
         <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="2"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2966,9 +3251,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2986,9 +3271,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2999,11 +3284,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -3019,24 +3309,31 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1466850</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>212864</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>42655</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5295900" cy="2895600"/>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>579783</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>118855</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D68405F-9914-44E7-8881-014955290287}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3049,25 +3346,32 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>66674</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>215346</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>8282</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4257675" cy="2876550"/>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>563217</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>84482</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD839AA6-955F-4EF0-B5EE-ADC5B6D37189}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3080,7 +3384,43 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>120098</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>127552</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>401706</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>13252</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3CBA88F-6563-764C-C02F-46691108EB7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3369,17 +3709,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="19.140625" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3402,11 +3745,23 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4">
         <v>120</v>
@@ -3421,13 +3776,29 @@
         <v>4.96</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="G2" s="6">
+        <f>B2*D2</f>
+        <v>19344</v>
+      </c>
+      <c r="H2" s="6">
+        <f>B2*C2</f>
+        <v>17820</v>
+      </c>
+      <c r="I2" s="6">
+        <f>B2*E2</f>
+        <v>595.20000000000005</v>
+      </c>
+      <c r="J2" s="7">
+        <f>IF(H2=0,0,I2/H2)</f>
+        <v>3.3400673400673403E-2</v>
       </c>
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4">
         <v>200</v>
@@ -3442,13 +3813,29 @@
         <v>1.94</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="G3" s="6">
+        <f>B3*D3</f>
+        <v>12460</v>
+      </c>
+      <c r="H3" s="6">
+        <f>B3*C3</f>
+        <v>11620</v>
+      </c>
+      <c r="I3" s="6">
+        <f>B3*E3</f>
+        <v>388</v>
+      </c>
+      <c r="J3" s="7">
+        <f>IF(H3=0,0,I3/H3)</f>
+        <v>3.3390705679862305E-2</v>
       </c>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4">
         <v>95</v>
@@ -3463,7 +3850,23 @@
         <v>4.03</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="G4" s="6">
+        <f>B4*D4</f>
+        <v>15019.5</v>
+      </c>
+      <c r="H4" s="6">
+        <f>B4*C4</f>
+        <v>13623</v>
+      </c>
+      <c r="I4" s="6">
+        <f>B4*E4</f>
+        <v>382.85</v>
+      </c>
+      <c r="J4" s="7">
+        <f>IF(H4=0,0,I4/H4)</f>
+        <v>2.8103207810320784E-2</v>
       </c>
       <c r="K4" s="1"/>
     </row>
@@ -3474,119 +3877,51 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
-        <f>B2*D2</f>
-        <v>19344</v>
-      </c>
-      <c r="B7" s="19">
-        <f>B2*C2</f>
-        <v>17820</v>
-      </c>
-      <c r="C7" s="6">
-        <f>B2*E2</f>
-        <v>595.20000000000005</v>
-      </c>
-      <c r="D7" s="7">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v>3.3400673400673403E-2</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
-        <f>B3*D3</f>
-        <v>12460</v>
-      </c>
-      <c r="B8" s="19">
-        <f>B3*C3</f>
-        <v>11620</v>
-      </c>
-      <c r="C8" s="6">
-        <f>B3*E3</f>
-        <v>388</v>
-      </c>
-      <c r="D8" s="7">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v>3.3390705679862305E-2</v>
+      <c r="A8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="12">
+        <f>SUM(G2:G4)</f>
+        <v>46823.5</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
-        <f>B4*D4</f>
-        <v>15019.5</v>
-      </c>
-      <c r="B9" s="19">
-        <f>B4*C4</f>
-        <v>13623</v>
-      </c>
-      <c r="C9" s="6">
-        <f>B4*E4</f>
-        <v>382.85</v>
-      </c>
-      <c r="D9" s="7">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v>2.8103207810320784E-2</v>
+      <c r="A9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(I2:I4)</f>
+        <v>1366.0500000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUMPRODUCT(J2:J4,H2:H4)/SUM(H2:H4)</f>
+        <v>3.1722128044957394E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="21">
-        <f>SUM(A7:A9)</f>
-        <v>46823.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="21">
-        <f>SUM(C7:C9)</f>
-        <v>1366.0500000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="22">
-        <f>SUMPRODUCT(D7:D9,B7:B9)/SUM(B7:B9)</f>
-        <v>3.1722128044957394E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="21">
-        <f>SUM(C7:C9)/12</f>
+      <c r="B11" s="12">
+        <f>SUM(I2:I4)/12</f>
         <v>113.83750000000002</v>
       </c>
     </row>
@@ -3605,49 +3940,56 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="17" customWidth="1"/>
-    <col min="3" max="10" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>46031</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>14</v>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C2" s="10">
         <f>'Holdings &amp; Settings'!B3</f>
@@ -3676,15 +4018,15 @@
         <v>201.61129568106313</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>46080</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>16</v>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C3" s="10">
         <f>'Holdings &amp; Settings'!B4</f>
@@ -3718,8 +4060,8 @@
       <c r="A4" s="9">
         <v>46093</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>11</v>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="10">
         <f>'Holdings &amp; Settings'!B2</f>
@@ -3748,15 +4090,15 @@
         <v>120.93350062735257</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>46122</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>14</v>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="10">
         <f t="shared" ref="C5:C13" si="2">I2</f>
@@ -3790,8 +4132,8 @@
       <c r="A6" s="9">
         <v>46170</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>16</v>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C6" s="10">
         <f t="shared" si="2"/>
@@ -3820,15 +4162,15 @@
         <v>95</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>46184</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>11</v>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" si="2"/>
@@ -3862,8 +4204,8 @@
       <c r="A8" s="9">
         <v>46214</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>14</v>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="2"/>
@@ -3892,15 +4234,15 @@
         <v>204.81236354559556</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>46261</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>16</v>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="2"/>
@@ -3934,8 +4276,8 @@
       <c r="A10" s="9">
         <v>46275</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>11</v>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
@@ -3969,8 +4311,8 @@
       <c r="A11" s="9">
         <v>46305</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>14</v>
+      <c r="B11" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C11" s="10">
         <f t="shared" si="2"/>
@@ -4004,8 +4346,8 @@
       <c r="A12" s="9">
         <v>46352</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>16</v>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
@@ -4034,15 +4376,15 @@
         <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>46366</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>11</v>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="2"/>
@@ -4082,44 +4424,46 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="25" t="s">
-        <v>38</v>
       </c>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=1)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4142,17 +4486,17 @@
         <v>416.6112956810631</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="26">
+      <c r="H2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="14">
         <f>SUM(B2:B13)</f>
         <v>1377.8837839604942</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=2)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4175,17 +4519,17 @@
         <v>416.6112956810631</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="27">
+      <c r="H3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="15">
         <f>SUM(C2:C13)</f>
         <v>10.140006856009196</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=3)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4208,17 +4552,17 @@
         <v>417.5447963084157</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="26">
+      <c r="H4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="14">
         <f>SUM(E2:E13)</f>
         <v>382.65999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=4)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4246,7 +4590,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=5)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4274,7 +4618,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=6)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4302,7 +4646,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=7)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4330,7 +4674,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=8)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4358,7 +4702,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=9)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4386,7 +4730,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=10)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4414,7 +4758,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=11)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4442,7 +4786,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="11">
         <f>SUMPRODUCT((MONTH('Dividend Log'!$A$2:$A$13)=12)*('Dividend Log'!$E$2:$E$13))</f>
@@ -4469,7 +4813,6 @@
       <c r="I13" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4480,14 +4823,18 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="12">
+      <c r="A1" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="17">
         <f>SUM('Holdings &amp; Settings'!B2:B4)</f>
         <v>415</v>
       </c>
@@ -4496,10 +4843,10 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="18">
         <f>'Reinvestment History'!F13</f>
         <v>425.14000685600922</v>
       </c>
@@ -4508,10 +4855,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="18">
         <f>'Reinvestment History'!I3</f>
         <v>10.140006856009196</v>
       </c>
@@ -4520,10 +4867,10 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="14">
+      <c r="A4" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="19">
         <f>SUM(C10:C12)</f>
         <v>1396.9936729855567</v>
       </c>
@@ -4532,10 +4879,10 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="A5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="20">
         <f>SUMPRODUCT(D10:D12,B10:B12)/SUM(B10:B12)</f>
         <v>3.3033817099476115E-2</v>
       </c>
@@ -4544,10 +4891,10 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="A6" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="19">
         <f>SUM(C10:C12)-SUM(E10:E12)</f>
         <v>30.943672985556532</v>
       </c>
@@ -4574,21 +4921,21 @@
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="10">
         <f>'Dividend Log'!I13</f>
@@ -4599,7 +4946,7 @@
         <v>613.71305166791342</v>
       </c>
       <c r="D10" s="7">
-        <f>IF('Holdings &amp; Settings'!B7=0,0,C10/'Holdings &amp; Settings'!B7)</f>
+        <f>IF('Holdings &amp; Settings'!H2=0,0,C10/'Holdings &amp; Settings'!H2)</f>
         <v>3.4439565188996261E-2</v>
       </c>
       <c r="E10" s="6">
@@ -4609,7 +4956,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="10">
         <f>'Dividend Log'!I11</f>
@@ -4620,7 +4967,7 @@
         <v>400.43062131764333</v>
       </c>
       <c r="D11" s="7">
-        <f>IF('Holdings &amp; Settings'!B8=0,0,C11/'Holdings &amp; Settings'!B8)</f>
+        <f>IF('Holdings &amp; Settings'!H3=0,0,C11/'Holdings &amp; Settings'!H3)</f>
         <v>3.4460466550571715E-2</v>
       </c>
       <c r="E11" s="6">
@@ -4630,7 +4977,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="10">
         <f>'Dividend Log'!I12</f>
@@ -4641,7 +4988,7 @@
         <v>382.85</v>
       </c>
       <c r="D12" s="7">
-        <f>IF('Holdings &amp; Settings'!B9=0,0,C12/'Holdings &amp; Settings'!B9)</f>
+        <f>IF('Holdings &amp; Settings'!H4=0,0,C12/'Holdings &amp; Settings'!H4)</f>
         <v>2.8103207810320784E-2</v>
       </c>
       <c r="E12" s="6">

--- a/sheets/investing/dividend-log/dividend-log.xlsx
+++ b/sheets/investing/dividend-log/dividend-log.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\000_drive_drive\300_WORK\xAI\002_xAI\project\excel-scraping\task_016\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\000_drive_drive\600_PROJECTS\modelstack\sheets\investing\dividend-log\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC41537F-68E3-4813-AA20-3ED69E3D4E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -228,7 +228,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -371,7 +371,7 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -386,7 +386,7 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -395,7 +395,7 @@
     <xf numFmtId="3" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1237,6 +1237,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-E6B4-4DED-84AD-E9DFD369E721}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1256,6 +1261,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-E6B4-4DED-84AD-E9DFD369E721}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1275,6 +1285,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-E6B4-4DED-84AD-E9DFD369E721}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
